--- a/euro-cordex-esgf.xlsx
+++ b/euro-cordex-esgf.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1126"/>
+  <dimension ref="A1:J1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>['mrso', 'prw', 'rsds', 'tasmax', 'ta850', 'mrros', 'ta500', 'rlds', 'ps', 'ua850', 'prc', 'hurs', 'sic', 'va200', 'hfls', 'rsdt', 'snc', 'cll', 'ua500', 'clm', 'clivi', 'huss', 'tauv', 'vas', 'va850', 'hfss', 'clh', 'clt', 'va500', 'evspsbl', 'rsut', 'snm', 'ua200', 'pr', 'tas', 'sfcWind', 'prsn', 'tasmin', 'mrro', 'clwvi']</t>
+          <t>['mrso', 'prw', 'rsds', 'tasmax', 'ta850', 'mrros', 'ta500', 'rlds', 'ps', 'ua850', 'prc', 'hurs', 'sic', 'va200', 'hfls', 'rsdt', 'snc', 'cll', 'ua500', 'clm', 'clivi', 'huss', 'tauv', 'vas', 'va850', 'hfss', 'clh', 'clt', 'va500', 'evspsbl', 'rsut', 'snm', 'ua200', 'pr', 'tas', 'sfcWind', 'prsn', 'tasmin', 'mrro', 'clwvi', 'tauu', 'sfcWindmax', 'rlus', 'psl', 'rsus', 'hus850', 'rlut', 'uas', 'ts', 'ta200']</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>['rsds', 'evspsbl', 'ta200', 'rlds', 'va500', 'tasmin', 'ua200', 'hurs', 'va850', 'snc', 'hfls', 'rsdt', 'hus850', 'sic', 'va200', 'clt', 'sfcWindmax', 'vas', 'ua500', 'hfss', 'tasmax', 'psl', 'snm', 'rsut', 'ua850', 'tas', 'ta500', 'mrro', 'uas', 'ta850']</t>
+          <t>['rsds', 'evspsbl', 'ta200', 'rlds', 'va500', 'tasmin', 'ua200', 'hurs', 'va850', 'snc', 'hfls', 'rsdt', 'hus850', 'sic', 'va200', 'clt', 'sfcWindmax', 'vas', 'ua500', 'hfss', 'tasmax', 'psl', 'snm', 'rsut', 'ua850', 'tas', 'ta500', 'mrro', 'uas', 'ta850', 'mrso', 'rlus', 'sfcWind', 'huss', 'pr', 'rsus', 'rlut', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>['sfcWind', 'tas', 'mrso', 'tasmax', 'rsds', 'uas', 'ta200', 'va850', 'clt', 'hurs', 'vas', 'hfls', 'rsdt', 'psl', 'sfcWindmax', 'snm', 'va500', 'rlds', 'ua200', 'evspsbl', 'ua850', 'rsut', 'rlus', 'va200', 'huss', 'snc', 'ua500', 'hfss', 'sic', 'rlut', 'mrro', 'ta850', 'rsus', 'ta500']</t>
+          <t>['sfcWind', 'tas', 'mrso', 'tasmax', 'rsds', 'uas', 'ta200', 'va850', 'clt', 'hurs', 'vas', 'hfls', 'rsdt', 'psl', 'sfcWindmax', 'snm', 'va500', 'rlds', 'ua200', 'evspsbl', 'ua850', 'rsut', 'rlus', 'va200', 'huss', 'snc', 'ua500', 'hfss', 'sic', 'rlut', 'mrro', 'ta850', 'rsus', 'ta500', 'pr', 'tasmin', 'mrros', 'hus850']</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>['cll', 'pr', 'snc', 'va500', 'prsn', 'rsus', 'prc', 'clivi', 'va850', 'ta200', 'sfcWindmax', 'tasmax', 'clwvi', 'ts', 'tauv', 'rsut', 'prw', 'rlus', 'huss', 'hfss', 'ta500', 'hurs', 'hfls', 'rsdt', 'hus850', 'rlds', 'ta850', 'sfcWind', 'mrros', 'tas', 'tasmin', 'evspsbl', 'ua500', 'snm', 'va200', 'mrso', 'psl', 'ua850', 'clt', 'rlut', 'sic', 'mrro']</t>
+          <t>['cll', 'pr', 'snc', 'va500', 'prsn', 'rsus', 'prc', 'clivi', 'va850', 'ta200', 'sfcWindmax', 'tasmax', 'clwvi', 'ts', 'tauv', 'rsut', 'prw', 'rlus', 'huss', 'hfss', 'ta500', 'hurs', 'hfls', 'rsdt', 'hus850', 'rlds', 'ta850', 'sfcWind', 'mrros', 'tas', 'tasmin', 'evspsbl', 'ua500', 'snm', 'va200', 'mrso', 'psl', 'ua850', 'clt', 'ua200', 'uas', 'tauu', 'clm', 'clh', 'vas', 'ps', 'rsds', 'rlut', 'sic', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>['sfcWind', 'sic', 'ua500', 'hus850', 'va200', 'pr', 'rsus', 'sfcWindmax', 'mrros', 'ta850', 'rsut', 'rlus', 'evspsbl', 'huss', 'ta500', 'hfss', 'hurs', 'hfls', 'rsdt', 'uas', 'rlds', 'ta200', 'tas', 'snm', 'vas', 'rsds', 'psl', 'ua850', 'mrro']</t>
+          <t>['sfcWind', 'sic', 'ua500', 'hus850', 'va200', 'pr', 'rsus', 'sfcWindmax', 'mrros', 'ta850', 'rsut', 'rlus', 'evspsbl', 'huss', 'ta500', 'hfss', 'hurs', 'hfls', 'rsdt', 'uas', 'rlds', 'ta200', 'tas', 'snm', 'vas', 'rsds', 'psl', 'tasmin', 'rlut', 'snc', 'va850', 'mrso', 'ua200', 'clt', 'tasmax', 'va500', 'ua850', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>['rsus', 'va200', 'rlut', 'ua850', 'clt', 'vas', 'mrro', 'psl', 'rlus', 'huss', 'ta500', 'hfss', 'uas', 'sfcWind', 'mrros', 'ta850', 'rsut', 'tas', 'tasmax', 'rlds', 'tasmin', 'ta200', 'hurs', 'sfcWindmax', 'hus850', 'hfls', 'rsdt', 'ua200', 'pr', 'mrso', 'snc', 'sic', 'snm', 'ua500']</t>
+          <t>['rsus', 'va200', 'rlut', 'ua850', 'clt', 'vas', 'mrro', 'psl', 'rlus', 'huss', 'ta500', 'hfss', 'uas', 'sfcWind', 'mrros', 'ta850', 'rsut', 'tas', 'tasmax', 'rlds', 'tasmin', 'ta200', 'hurs', 'sfcWindmax', 'hus850', 'hfls', 'rsdt', 'ua200', 'pr', 'mrso', 'snc', 'sic', 'evspsbl', 'rsds', 'va500', 'va850', 'snm', 'ua500']</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>['pr', 'ps']</t>
+          <t>['pr', 'ps', 'tas', 'rsus', 'sfcWind', 'huss', 'rsds', 'hurs', 'psl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -24037,7 +24037,7 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>['psl', 'clt', 'rlds', 'ta850', 'vas', 'ta500', 'rsds', 'hurs', 'snw', 'mrro', 'va500', 'rsus', 'rlut', 'huss', 'tasmin', 'tas', 'sfcWind', 'tasmax', 'pr']</t>
+          <t>['psl', 'clt', 'rlds', 'ta850', 'vas', 'ta500', 'rsds', 'hurs', 'snw', 'mrro', 'va500', 'rsus', 'rlut', 'huss', 'prc', 'ps', 'ua500', 'ua850', 'ts', 'va850', 'wsgsmax', 'uas', 'prsn', 'rlus', 'hfss', 'rsdt', 'evspsbl', 'zg500', 'sfcWindmax', 'hfls', 'mrso', 'rsut', 'hus850', 'ta200', 'tasmin', 'tas', 'sfcWind', 'tasmax', 'pr']</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'ta850', 'sfcWindmax', 'evspsbl', 'huss', 'clt', 'sfcWind', 'vas', 'zg500', 'ta500', 'va500', 'va850', 'hfls', 'rsus', 'rlus', 'hurs', 'pr', 'mrso', 'ta200', 'rsut']</t>
+          <t>['rsds', 'rlds', 'ta850', 'sfcWindmax', 'evspsbl', 'huss', 'clt', 'sfcWind', 'vas', 'zg500', 'ta500', 'va500', 'va850', 'hfls', 'rsus', 'rlus', 'hurs', 'pr', 'mrso', 'ta200', 'rsut', 'hus850', 'ua500', 'tasmax', 'hfss', 'psl', 'uas', 'rsdt', 'rlut', 'snw', 'ua850', 'tas', 'mrro', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -24101,7 +24101,7 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>['tas', 'zg500', 'hfss', 'pr', 'hfls', 'rlut', 'evspsbl', 'rsds', 'mrso', 'ta500', 'rlus', 'clt', 'mrro', 'rsdt', 'rsut', 'sfcWind', 'ta200', 'sfcWindmax']</t>
+          <t>['tas', 'zg500', 'hfss', 'pr', 'hfls', 'rlut', 'evspsbl', 'rsds', 'mrso', 'ta500', 'rlus', 'clt', 'mrro', 'rsdt', 'rsut', 'sfcWind', 'ta200', 'sfcWindmax', 'ta850', 'ua850', 'tasmin', 'tasmax', 'huss', 'snw', 'psl', 'rlds', 'va850', 'ua500', 'rsus', 'uas', 'hurs', 'vas', 'hus850', 'va500']</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>['ta500', 'rlus', 'ta850', 'ua500', 'prc', 'uas', 'ta200', 'rsut', 'sund', 'prsn', 'snd', 'ua850', 'tasmin', 'tas', 'rsds', 'huss', 'sfcWind', 'pr', 'ps', 'tasmax', 'clt', 'zg500', 'rsus', 'hurs', 'evspsbl', 'va850', 'rlds', 'psl']</t>
+          <t>['va500', 'hus850', 'rsdt', 'snc', 'rlut', 'prhmax', 'vas', 'wsgsmax', 'mrro', 'snw', 'hfss', 'hfls', 'mrso', 'ts', 'sfcWindmax', 'ta500', 'rlus', 'ta850', 'ua500', 'prc', 'uas', 'ta200', 'rsut', 'sund', 'prsn', 'snd', 'ua850', 'tasmin', 'tas', 'rsds', 'huss', 'sfcWind', 'pr', 'ps', 'tasmax', 'clt', 'zg500', 'rsus', 'hurs', 'evspsbl', 'va850', 'rlds', 'psl']</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'sftgif']</t>
+          <t>['areacella', 'orog', 'sftlf', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25273,7 +25273,7 @@
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>['snc', 'ta200', 'vas', 'rlus', 'ua500', 'ua850', 'rsds', 'hurs', 'pr', 'clt', 'tasmax', 'va850', 'huss', 'rlds', 'psl', 'zg500', 'sfcWind', 'tasmin', 'tas', 'rsus', 'evspsbl']</t>
+          <t>['ta850', 'hfls', 'rsdt', 'snw', 'sund', 'sfcWindmax', 'mrso', 'snd', 'va500', 'mrro', 'hfss', 'hus850', 'rlut', 'uas', 'ta500', 'rsut', 'snc', 'ta200', 'vas', 'rlus', 'ua500', 'ua850', 'rsds', 'hurs', 'pr', 'clt', 'tasmax', 'va850', 'huss', 'rlds', 'psl', 'zg500', 'sfcWind', 'tasmin', 'tas', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>['ta200', 'va500', 'rlut', 'sund', 'tas', 'clt', 'tasmax', 'tasmin', 'ua850', 'zg500', 'rsus', 'evspsbl', 'hurs', 'pr', 'rsds', 'sfcWind', 'huss', 'psl', 'va850', 'rlds']</t>
+          <t>['vas', 'rlus', 'ta500', 'snw', 'uas', 'rsut', 'snd', 'ua500', 'ta850', 'hfss', 'sfcWindmax', 'snc', 'hfls', 'hus850', 'mrso', 'rsdt', 'mrro', 'ta200', 'va500', 'rlut', 'sund', 'tas', 'clt', 'tasmax', 'tasmin', 'ua850', 'zg500', 'rsus', 'evspsbl', 'hurs', 'pr', 'rsds', 'sfcWind', 'huss', 'psl', 'va850', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>['rsdt', 'sund', 'hfss', 'hfls', 'prsn', 'mrso', 'pr', 'ua850', 'tasmin', 'rlds', 'va850', 'rsus', 'evspsbl', 'rsds', 'clt', 'psl', 'huss', 'sfcWind', 'ps', 'tas', 'zg500', 'hurs', 'tasmax']</t>
+          <t>['prc', 'snw', 'ua500', 'uas', 'snd', 'vas', 'rsut', 'mrro', 'ta200', 'snc', 'hus850', 'ta850', 'wsgsmax', 'va500', 'sfcWindmax', 'rlut', 'ta500', 'prhmax', 'ts', 'rlus', 'rsdt', 'sund', 'hfss', 'hfls', 'prsn', 'mrso', 'pr', 'ua850', 'tasmin', 'rlds', 'va850', 'rsus', 'evspsbl', 'rsds', 'clt', 'psl', 'huss', 'sfcWind', 'ps', 'tas', 'zg500', 'hurs', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftgif']</t>
+          <t>['areacella', 'sftlf', 'orog', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25873,7 +25873,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>['ta850', 'rsut', 'snw', 'snd', 'rlus', 'sund', 'clt', 'rlds', 'psl', 'huss', 'rsus', 'rsds', 'evspsbl', 'tasmax', 'va850', 'tas', 'tasmin', 'ua850', 'zg500', 'hurs', 'sfcWind', 'pr']</t>
+          <t>['hfss', 'sfcWindmax', 'snc', 'rlut', 'ta200', 'hfls', 'vas', 'mrro', 'mrso', 'uas', 'ta500', 'ua500', 'hus850', 'rsdt', 'va500', 'ta850', 'rsut', 'snw', 'snd', 'rlus', 'sund', 'clt', 'rlds', 'psl', 'huss', 'rsus', 'rsds', 'evspsbl', 'tasmax', 'va850', 'tas', 'tasmin', 'ua850', 'zg500', 'hurs', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>['rlus', 'hus850', 'hfls', 'rlut', 'ta200', 'sund', 'tasmin', 'pr', 'rsds', 'tasmax', 'rsus', 'zg500', 'clt', 'ua850', 'tas', 'hurs', 'psl', 'va850', 'huss', 'evspsbl', 'sfcWind', 'rlds']</t>
+          <t>['snd', 'ua500', 'ta500', 'rsut', 'snw', 'uas', 'mrso', 'sfcWindmax', 'vas', 'rsdt', 'va500', 'mrro', 'hfss', 'snc', 'ta850', 'rlus', 'hus850', 'hfls', 'rlut', 'ta200', 'sund', 'tasmin', 'pr', 'rsds', 'tasmax', 'rsus', 'zg500', 'clt', 'ua850', 'tas', 'hurs', 'psl', 'va850', 'huss', 'evspsbl', 'sfcWind', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36300,17 +36300,17 @@
     <row r="1101">
       <c r="A1101" s="1" t="inlineStr">
         <is>
-          <t>SMHI</t>
+          <t>UHOH</t>
         </is>
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>RCA4</t>
+          <t>WRF361H</t>
         </is>
       </c>
       <c r="C1101" s="1" t="inlineStr">
         <is>
-          <t>IPSL-IPSL-CM5A-MR</t>
+          <t>MPI-M-MPI-ESM-LR</t>
         </is>
       </c>
       <c r="D1101" s="1" t="inlineStr">
@@ -36320,22 +36320,22 @@
       </c>
       <c r="E1101" s="1" t="inlineStr">
         <is>
-          <t>r1i1p1</t>
+          <t>r0i0p0</t>
         </is>
       </c>
       <c r="F1101" s="1" t="inlineStr">
         <is>
-          <t>sem</t>
+          <t>fx</t>
         </is>
       </c>
       <c r="G1101" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20170524</t>
         </is>
       </c>
       <c r="H1101" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1101" s="1" t="inlineStr">
@@ -36345,41 +36345,33 @@
       </c>
       <c r="J1101" t="inlineStr">
         <is>
-          <t>['vas', 'zg200', 'uas', 'va200', 'ua500', 'rlus', 'hfss', 'huss', 'psl', 'hus850', 'mrro', 'clt']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" s="1" t="n"/>
       <c r="B1102" s="1" t="n"/>
-      <c r="C1102" s="1" t="inlineStr">
-        <is>
-          <t>MOHC-HadGEM2-ES</t>
-        </is>
-      </c>
-      <c r="D1102" s="1" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
+      <c r="C1102" s="1" t="n"/>
+      <c r="D1102" s="1" t="n"/>
       <c r="E1102" s="1" t="inlineStr">
         <is>
-          <t>r0i0p0</t>
+          <t>r1i1p1</t>
         </is>
       </c>
       <c r="F1102" s="1" t="inlineStr">
         <is>
-          <t>fx</t>
+          <t>day</t>
         </is>
       </c>
       <c r="G1102" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20170524</t>
         </is>
       </c>
       <c r="H1102" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1102" s="1" t="inlineStr">
@@ -36389,7 +36381,7 @@
       </c>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog']</t>
+          <t>['sfcWind', 'tasmax', 'pr', 'tasmin', 'tas']</t>
         </is>
       </c>
     </row>
@@ -36398,24 +36390,16 @@
       <c r="B1103" s="1" t="n"/>
       <c r="C1103" s="1" t="n"/>
       <c r="D1103" s="1" t="n"/>
-      <c r="E1103" s="1" t="inlineStr">
-        <is>
-          <t>r1i1p1</t>
-        </is>
-      </c>
-      <c r="F1103" s="1" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
+      <c r="E1103" s="1" t="n"/>
+      <c r="F1103" s="1" t="n"/>
       <c r="G1103" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20180717</t>
         </is>
       </c>
       <c r="H1103" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1103" s="1" t="inlineStr">
@@ -36425,7 +36409,7 @@
       </c>
       <c r="J1103" t="inlineStr">
         <is>
-          <t>['rsus', 'prhmax', 'rlus', 'rlut', 'prc', 'huss', 'prsn', 'mrro', 'pr', 'hfss', 'cll', 'tasmax', 'tauv', 'rsut', 'snc', 'sic', 'sund']</t>
+          <t>['uas', 'huss']</t>
         </is>
       </c>
     </row>
@@ -36435,19 +36419,15 @@
       <c r="C1104" s="1" t="n"/>
       <c r="D1104" s="1" t="n"/>
       <c r="E1104" s="1" t="n"/>
-      <c r="F1104" s="1" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
+      <c r="F1104" s="1" t="n"/>
       <c r="G1104" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20190304</t>
         </is>
       </c>
       <c r="H1104" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1104" s="1" t="inlineStr">
@@ -36457,7 +36437,7 @@
       </c>
       <c r="J1104" t="inlineStr">
         <is>
-          <t>['rsus', 'rlus', 'rlut', 'snc', 'sic', 'va850', 'mrro', 'ta200', 'pr']</t>
+          <t>['mrso', 'evspsbl', 'prc', 'prsn', 'mrro', 'ps', 'snw', 'vas', 'snc', 'ts', 'snd']</t>
         </is>
       </c>
     </row>
@@ -36467,19 +36447,15 @@
       <c r="C1105" s="1" t="n"/>
       <c r="D1105" s="1" t="n"/>
       <c r="E1105" s="1" t="n"/>
-      <c r="F1105" s="1" t="inlineStr">
-        <is>
-          <t>sem</t>
-        </is>
-      </c>
+      <c r="F1105" s="1" t="n"/>
       <c r="G1105" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20191105</t>
         </is>
       </c>
       <c r="H1105" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1105" s="1" t="inlineStr">
@@ -36489,7 +36465,7 @@
       </c>
       <c r="J1105" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsus', 'hfss', 'rsut', 'rlut', 'sfcWind', 'psl', 'mrro', 'clt']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36497,29 +36473,21 @@
       <c r="A1106" s="1" t="n"/>
       <c r="B1106" s="1" t="n"/>
       <c r="C1106" s="1" t="n"/>
-      <c r="D1106" s="1" t="inlineStr">
-        <is>
-          <t>rcp45</t>
-        </is>
-      </c>
-      <c r="E1106" s="1" t="inlineStr">
-        <is>
-          <t>r1i1p1</t>
-        </is>
-      </c>
+      <c r="D1106" s="1" t="n"/>
+      <c r="E1106" s="1" t="n"/>
       <c r="F1106" s="1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="G1106" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20170524</t>
         </is>
       </c>
       <c r="H1106" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1106" s="1" t="inlineStr">
@@ -36529,7 +36497,7 @@
       </c>
       <c r="J1106" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsds', 'rlds', 'prhmax', 'mrso', 'cll', 'sfcWind', 'prw', 'sic']</t>
+          <t>['tasmin', 'tasmax', 'sfcWind', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36539,19 +36507,15 @@
       <c r="C1107" s="1" t="n"/>
       <c r="D1107" s="1" t="n"/>
       <c r="E1107" s="1" t="n"/>
-      <c r="F1107" s="1" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
+      <c r="F1107" s="1" t="n"/>
       <c r="G1107" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20180717</t>
         </is>
       </c>
       <c r="H1107" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1107" s="1" t="inlineStr">
@@ -36561,7 +36525,7 @@
       </c>
       <c r="J1107" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsds', 'rlds', 'hfls', 'rsdt', 'mrfso', 'mrso', 'hus850', 'sic']</t>
+          <t>['uas', 'huss']</t>
         </is>
       </c>
     </row>
@@ -36571,19 +36535,15 @@
       <c r="C1108" s="1" t="n"/>
       <c r="D1108" s="1" t="n"/>
       <c r="E1108" s="1" t="n"/>
-      <c r="F1108" s="1" t="inlineStr">
-        <is>
-          <t>sem</t>
-        </is>
-      </c>
+      <c r="F1108" s="1" t="n"/>
       <c r="G1108" s="1" t="inlineStr">
         <is>
-          <t>v20131026</t>
+          <t>v20190304</t>
         </is>
       </c>
       <c r="H1108" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1108" s="1" t="inlineStr">
@@ -36593,41 +36553,25 @@
       </c>
       <c r="J1108" t="inlineStr">
         <is>
-          <t>['rsds', 'tasmax', 'rsdt', 'snm', 'uas', 'tas', 'va850', 'ta200', 'pr']</t>
+          <t>['evspsbl', 'mrro', 'mrso', 'vas', 'snw', 'snc', 'snd']</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" s="1" t="n"/>
       <c r="B1109" s="1" t="n"/>
-      <c r="C1109" s="1" t="inlineStr">
-        <is>
-          <t>MPI-M-MPI-ESM-LR</t>
-        </is>
-      </c>
-      <c r="D1109" s="1" t="inlineStr">
-        <is>
-          <t>rcp85</t>
-        </is>
-      </c>
-      <c r="E1109" s="1" t="inlineStr">
-        <is>
-          <t>r1i1p1</t>
-        </is>
-      </c>
-      <c r="F1109" s="1" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
+      <c r="C1109" s="1" t="n"/>
+      <c r="D1109" s="1" t="n"/>
+      <c r="E1109" s="1" t="n"/>
+      <c r="F1109" s="1" t="n"/>
       <c r="G1109" s="1" t="inlineStr">
         <is>
-          <t>v20160803</t>
+          <t>v20191105</t>
         </is>
       </c>
       <c r="H1109" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1109" s="1" t="inlineStr">
@@ -36637,7 +36581,7 @@
       </c>
       <c r="J1109" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'prhmax', 'rlus', 'rlut', 'prw', 'psl', 'prsn', 'ps', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'sic', 'snd', 'tasmax', 'tasmin', 'tauv', 'tauu', 'tas', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va200', 'va500', 'va850', 'ua200', 'ua500', 'ua850', 'ts', 'wsgsmax', 'zmla', 'zg500', 'zg200']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36647,19 +36591,15 @@
       <c r="C1110" s="1" t="n"/>
       <c r="D1110" s="1" t="n"/>
       <c r="E1110" s="1" t="n"/>
-      <c r="F1110" s="1" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
+      <c r="F1110" s="1" t="n"/>
       <c r="G1110" s="1" t="inlineStr">
         <is>
-          <t>v20160803</t>
+          <t>v20191119</t>
         </is>
       </c>
       <c r="H1110" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1110" s="1" t="inlineStr">
@@ -36669,7 +36609,7 @@
       </c>
       <c r="J1110" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'hurs', 'clt', 'rlds', 'rlus', 'mrfso', 'mrso', 'huss', 'psl', 'hus850', 'mrro', 'pr', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'sic', 'tasmax', 'tasmin', 'snm', 'tas', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'zg200', 'va200', 'va500', 'va850', 'ua200', 'ua850', 'ua500', 'zg500']</t>
+          <t>['clivi', 'zmla', 'ts', 'clwvi', 'prc', 'prw', 'prsn', 'ps']</t>
         </is>
       </c>
     </row>
@@ -36686,12 +36626,12 @@
       </c>
       <c r="G1111" s="1" t="inlineStr">
         <is>
-          <t>v20160803</t>
+          <t>v20170524</t>
         </is>
       </c>
       <c r="H1111" s="1" t="inlineStr">
         <is>
-          <t>esg-dn1.nsc.liu.se</t>
+          <t>esgf1.dkrz.de</t>
         </is>
       </c>
       <c r="I1111" s="1" t="inlineStr">
@@ -36701,44 +36641,20 @@
       </c>
       <c r="J1111" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'evspsbl', 'huss', 'hurs', 'hus850', 'clt', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'sund', 'snc', 'sic', 'snd', 'tasmax', 'tasmin', 'tas', 'ta200', 'ta850', 'ta500', 'ua200', 'ua500', 'ua850', 'vas', 'uas', 'zg200', 'zg500', 'va200', 'va500', 'va850']</t>
+          <t>['pr', 'tasmin', 'sfcWind', 'tas', 'tasmax']</t>
         </is>
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" s="1" t="inlineStr">
-        <is>
-          <t>UHOH</t>
-        </is>
-      </c>
-      <c r="B1112" s="1" t="inlineStr">
-        <is>
-          <t>WRF361H</t>
-        </is>
-      </c>
-      <c r="C1112" s="1" t="inlineStr">
-        <is>
-          <t>MPI-M-MPI-ESM-LR</t>
-        </is>
-      </c>
-      <c r="D1112" s="1" t="inlineStr">
-        <is>
-          <t>rcp85</t>
-        </is>
-      </c>
-      <c r="E1112" s="1" t="inlineStr">
-        <is>
-          <t>r0i0p0</t>
-        </is>
-      </c>
-      <c r="F1112" s="1" t="inlineStr">
-        <is>
-          <t>fx</t>
-        </is>
-      </c>
+      <c r="A1112" s="1" t="n"/>
+      <c r="B1112" s="1" t="n"/>
+      <c r="C1112" s="1" t="n"/>
+      <c r="D1112" s="1" t="n"/>
+      <c r="E1112" s="1" t="n"/>
+      <c r="F1112" s="1" t="n"/>
       <c r="G1112" s="1" t="inlineStr">
         <is>
-          <t>v20170524</t>
+          <t>v20180717</t>
         </is>
       </c>
       <c r="H1112" s="1" t="inlineStr">
@@ -36753,7 +36669,7 @@
       </c>
       <c r="J1112" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog']</t>
+          <t>['uas', 'huss']</t>
         </is>
       </c>
     </row>
@@ -36762,19 +36678,11 @@
       <c r="B1113" s="1" t="n"/>
       <c r="C1113" s="1" t="n"/>
       <c r="D1113" s="1" t="n"/>
-      <c r="E1113" s="1" t="inlineStr">
-        <is>
-          <t>r1i1p1</t>
-        </is>
-      </c>
-      <c r="F1113" s="1" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
+      <c r="E1113" s="1" t="n"/>
+      <c r="F1113" s="1" t="n"/>
       <c r="G1113" s="1" t="inlineStr">
         <is>
-          <t>v20170524</t>
+          <t>v20190304</t>
         </is>
       </c>
       <c r="H1113" s="1" t="inlineStr">
@@ -36789,7 +36697,7 @@
       </c>
       <c r="J1113" t="inlineStr">
         <is>
-          <t>['sfcWind', 'tasmax', 'pr', 'tasmin', 'tas']</t>
+          <t>['evspsbl', 'mrso', 'vas', 'snw', 'snc', 'mrro', 'snd']</t>
         </is>
       </c>
     </row>
@@ -36802,7 +36710,7 @@
       <c r="F1114" s="1" t="n"/>
       <c r="G1114" s="1" t="inlineStr">
         <is>
-          <t>v20180717</t>
+          <t>v20191105</t>
         </is>
       </c>
       <c r="H1114" s="1" t="inlineStr">
@@ -36817,7 +36725,7 @@
       </c>
       <c r="J1114" t="inlineStr">
         <is>
-          <t>['uas', 'huss']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36830,7 +36738,7 @@
       <c r="F1115" s="1" t="n"/>
       <c r="G1115" s="1" t="inlineStr">
         <is>
-          <t>v20190304</t>
+          <t>v20191119</t>
         </is>
       </c>
       <c r="H1115" s="1" t="inlineStr">
@@ -36845,328 +36753,12 @@
       </c>
       <c r="J1115" t="inlineStr">
         <is>
-          <t>['mrso', 'evspsbl', 'prc', 'prsn', 'mrro', 'ps', 'snw', 'vas', 'snc', 'ts', 'snd']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" s="1" t="n"/>
-      <c r="B1116" s="1" t="n"/>
-      <c r="C1116" s="1" t="n"/>
-      <c r="D1116" s="1" t="n"/>
-      <c r="E1116" s="1" t="n"/>
-      <c r="F1116" s="1" t="n"/>
-      <c r="G1116" s="1" t="inlineStr">
-        <is>
-          <t>v20191105</t>
-        </is>
-      </c>
-      <c r="H1116" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1116" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1116" t="inlineStr">
-        <is>
-          <t>['rsds', 'rlds']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1117">
-      <c r="A1117" s="1" t="n"/>
-      <c r="B1117" s="1" t="n"/>
-      <c r="C1117" s="1" t="n"/>
-      <c r="D1117" s="1" t="n"/>
-      <c r="E1117" s="1" t="n"/>
-      <c r="F1117" s="1" t="inlineStr">
-        <is>
-          <t>mon</t>
-        </is>
-      </c>
-      <c r="G1117" s="1" t="inlineStr">
-        <is>
-          <t>v20170524</t>
-        </is>
-      </c>
-      <c r="H1117" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1117" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1117" t="inlineStr">
-        <is>
-          <t>['tasmin', 'tasmax', 'sfcWind', 'tas', 'pr']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1118">
-      <c r="A1118" s="1" t="n"/>
-      <c r="B1118" s="1" t="n"/>
-      <c r="C1118" s="1" t="n"/>
-      <c r="D1118" s="1" t="n"/>
-      <c r="E1118" s="1" t="n"/>
-      <c r="F1118" s="1" t="n"/>
-      <c r="G1118" s="1" t="inlineStr">
-        <is>
-          <t>v20180717</t>
-        </is>
-      </c>
-      <c r="H1118" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1118" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1118" t="inlineStr">
-        <is>
-          <t>['uas', 'huss']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" s="1" t="n"/>
-      <c r="B1119" s="1" t="n"/>
-      <c r="C1119" s="1" t="n"/>
-      <c r="D1119" s="1" t="n"/>
-      <c r="E1119" s="1" t="n"/>
-      <c r="F1119" s="1" t="n"/>
-      <c r="G1119" s="1" t="inlineStr">
-        <is>
-          <t>v20190304</t>
-        </is>
-      </c>
-      <c r="H1119" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1119" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1119" t="inlineStr">
-        <is>
-          <t>['evspsbl', 'mrro', 'mrso', 'vas', 'snw', 'snc', 'snd']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" s="1" t="n"/>
-      <c r="B1120" s="1" t="n"/>
-      <c r="C1120" s="1" t="n"/>
-      <c r="D1120" s="1" t="n"/>
-      <c r="E1120" s="1" t="n"/>
-      <c r="F1120" s="1" t="n"/>
-      <c r="G1120" s="1" t="inlineStr">
-        <is>
-          <t>v20191105</t>
-        </is>
-      </c>
-      <c r="H1120" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1120" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1120" t="inlineStr">
-        <is>
-          <t>['rsds', 'rlds']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" s="1" t="n"/>
-      <c r="B1121" s="1" t="n"/>
-      <c r="C1121" s="1" t="n"/>
-      <c r="D1121" s="1" t="n"/>
-      <c r="E1121" s="1" t="n"/>
-      <c r="F1121" s="1" t="n"/>
-      <c r="G1121" s="1" t="inlineStr">
-        <is>
-          <t>v20191119</t>
-        </is>
-      </c>
-      <c r="H1121" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1121" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1121" t="inlineStr">
-        <is>
-          <t>['clivi', 'zmla', 'ts', 'clwvi', 'prc', 'prw', 'prsn', 'ps']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" s="1" t="n"/>
-      <c r="B1122" s="1" t="n"/>
-      <c r="C1122" s="1" t="n"/>
-      <c r="D1122" s="1" t="n"/>
-      <c r="E1122" s="1" t="n"/>
-      <c r="F1122" s="1" t="inlineStr">
-        <is>
-          <t>sem</t>
-        </is>
-      </c>
-      <c r="G1122" s="1" t="inlineStr">
-        <is>
-          <t>v20170524</t>
-        </is>
-      </c>
-      <c r="H1122" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1122" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1122" t="inlineStr">
-        <is>
-          <t>['pr', 'tasmin', 'sfcWind', 'tas', 'tasmax']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" s="1" t="n"/>
-      <c r="B1123" s="1" t="n"/>
-      <c r="C1123" s="1" t="n"/>
-      <c r="D1123" s="1" t="n"/>
-      <c r="E1123" s="1" t="n"/>
-      <c r="F1123" s="1" t="n"/>
-      <c r="G1123" s="1" t="inlineStr">
-        <is>
-          <t>v20180717</t>
-        </is>
-      </c>
-      <c r="H1123" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1123" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1123" t="inlineStr">
-        <is>
-          <t>['uas', 'huss']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" s="1" t="n"/>
-      <c r="B1124" s="1" t="n"/>
-      <c r="C1124" s="1" t="n"/>
-      <c r="D1124" s="1" t="n"/>
-      <c r="E1124" s="1" t="n"/>
-      <c r="F1124" s="1" t="n"/>
-      <c r="G1124" s="1" t="inlineStr">
-        <is>
-          <t>v20190304</t>
-        </is>
-      </c>
-      <c r="H1124" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1124" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1124" t="inlineStr">
-        <is>
-          <t>['evspsbl', 'mrso', 'vas', 'snw', 'snc', 'mrro', 'snd']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1125">
-      <c r="A1125" s="1" t="n"/>
-      <c r="B1125" s="1" t="n"/>
-      <c r="C1125" s="1" t="n"/>
-      <c r="D1125" s="1" t="n"/>
-      <c r="E1125" s="1" t="n"/>
-      <c r="F1125" s="1" t="n"/>
-      <c r="G1125" s="1" t="inlineStr">
-        <is>
-          <t>v20191105</t>
-        </is>
-      </c>
-      <c r="H1125" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1125" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1125" t="inlineStr">
-        <is>
-          <t>['rsds', 'rlds']</t>
-        </is>
-      </c>
-    </row>
-    <row r="1126">
-      <c r="A1126" s="1" t="n"/>
-      <c r="B1126" s="1" t="n"/>
-      <c r="C1126" s="1" t="n"/>
-      <c r="D1126" s="1" t="n"/>
-      <c r="E1126" s="1" t="n"/>
-      <c r="F1126" s="1" t="n"/>
-      <c r="G1126" s="1" t="inlineStr">
-        <is>
-          <t>v20191119</t>
-        </is>
-      </c>
-      <c r="H1126" s="1" t="inlineStr">
-        <is>
-          <t>esgf1.dkrz.de</t>
-        </is>
-      </c>
-      <c r="I1126" s="1" t="inlineStr">
-        <is>
-          <t>EUR-11</t>
-        </is>
-      </c>
-      <c r="J1126" t="inlineStr">
-        <is>
           <t>['prw', 'prsn', 'ps', 'clwvi', 'prc', 'clivi', 'zmla', 'ts']</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="525">
+  <mergeCells count="515">
     <mergeCell ref="E926:E931"/>
     <mergeCell ref="E685:E687"/>
     <mergeCell ref="E1025:E1031"/>
@@ -37187,13 +36779,10 @@
     <mergeCell ref="F386:F389"/>
     <mergeCell ref="D541:D558"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="A1112:A1126"/>
-    <mergeCell ref="F1113:F1116"/>
     <mergeCell ref="C1039:C1052"/>
     <mergeCell ref="D1012:D1024"/>
     <mergeCell ref="F1012:F1013"/>
     <mergeCell ref="C761:C784"/>
-    <mergeCell ref="E1103:E1105"/>
     <mergeCell ref="D109:D115"/>
     <mergeCell ref="C31:C55"/>
     <mergeCell ref="F514:F517"/>
@@ -37246,7 +36835,6 @@
     <mergeCell ref="F549:F553"/>
     <mergeCell ref="D702:D708"/>
     <mergeCell ref="E284:E290"/>
-    <mergeCell ref="E1106:E1108"/>
     <mergeCell ref="E853:E858"/>
     <mergeCell ref="E482:E498"/>
     <mergeCell ref="F324:F327"/>
@@ -37288,7 +36876,6 @@
     <mergeCell ref="F428:F432"/>
     <mergeCell ref="E659:E661"/>
     <mergeCell ref="D343:D366"/>
-    <mergeCell ref="E1109:E1111"/>
     <mergeCell ref="C264:C269"/>
     <mergeCell ref="C74:C95"/>
     <mergeCell ref="E264:E269"/>
@@ -37297,7 +36884,7 @@
     <mergeCell ref="E225:E227"/>
     <mergeCell ref="D1005:D1011"/>
     <mergeCell ref="D88:D95"/>
-    <mergeCell ref="F1117:F1121"/>
+    <mergeCell ref="A1101:A1115"/>
     <mergeCell ref="D571:D587"/>
     <mergeCell ref="F86:F87"/>
     <mergeCell ref="D715:D721"/>
@@ -37306,6 +36893,7 @@
     <mergeCell ref="C499:C510"/>
     <mergeCell ref="C959:C991"/>
     <mergeCell ref="E703:E708"/>
+    <mergeCell ref="E1102:E1115"/>
     <mergeCell ref="E1032:E1038"/>
     <mergeCell ref="F808:F809"/>
     <mergeCell ref="D877:D882"/>
@@ -37353,6 +36941,7 @@
     <mergeCell ref="E710:E714"/>
     <mergeCell ref="F360:F366"/>
     <mergeCell ref="F992:F993"/>
+    <mergeCell ref="F1111:F1115"/>
     <mergeCell ref="E535:E540"/>
     <mergeCell ref="A313:A621"/>
     <mergeCell ref="E10:E16"/>
@@ -37368,7 +36957,6 @@
     <mergeCell ref="E89:E95"/>
     <mergeCell ref="E278:E283"/>
     <mergeCell ref="F242:F243"/>
-    <mergeCell ref="C1102:C1108"/>
     <mergeCell ref="E883:E888"/>
     <mergeCell ref="D773:D778"/>
     <mergeCell ref="D767:D772"/>
@@ -37423,6 +37011,7 @@
     <mergeCell ref="C1057:C1084"/>
     <mergeCell ref="F1021:F1022"/>
     <mergeCell ref="E1039:E1045"/>
+    <mergeCell ref="D1101:D1115"/>
     <mergeCell ref="F453:F457"/>
     <mergeCell ref="F948:F949"/>
     <mergeCell ref="C643:C646"/>
@@ -37433,7 +37022,6 @@
     <mergeCell ref="E297:E302"/>
     <mergeCell ref="F519:F523"/>
     <mergeCell ref="E902:E907"/>
-    <mergeCell ref="B1101:B1111"/>
     <mergeCell ref="F968:F969"/>
     <mergeCell ref="D972:D978"/>
     <mergeCell ref="D42:D48"/>
@@ -37470,12 +37058,12 @@
     <mergeCell ref="F494:F498"/>
     <mergeCell ref="E193:E199"/>
     <mergeCell ref="D222:D224"/>
-    <mergeCell ref="C1109:C1111"/>
     <mergeCell ref="D511:D528"/>
     <mergeCell ref="F1016:F1017"/>
     <mergeCell ref="F423:F427"/>
     <mergeCell ref="E920:E925"/>
     <mergeCell ref="F391:F394"/>
+    <mergeCell ref="C1101:C1115"/>
     <mergeCell ref="E605:E621"/>
     <mergeCell ref="E648:E650"/>
     <mergeCell ref="C753:C756"/>
@@ -37528,6 +37116,7 @@
     <mergeCell ref="E623:E628"/>
     <mergeCell ref="B219:B233"/>
     <mergeCell ref="D920:D925"/>
+    <mergeCell ref="B1101:B1115"/>
     <mergeCell ref="D605:D621"/>
     <mergeCell ref="E908:E913"/>
     <mergeCell ref="D1078:D1084"/>
@@ -37555,7 +37144,6 @@
     <mergeCell ref="D309:D312"/>
     <mergeCell ref="D2:D8"/>
     <mergeCell ref="D992:D1004"/>
-    <mergeCell ref="A1101:A1111"/>
     <mergeCell ref="C284:C296"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="D187:D205"/>
@@ -37565,9 +37153,8 @@
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="E667:E672"/>
     <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C1112:C1126"/>
+    <mergeCell ref="F440:F444"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="F440:F444"/>
     <mergeCell ref="C757:C758"/>
     <mergeCell ref="E71:E73"/>
     <mergeCell ref="E1068:E1070"/>
@@ -37578,18 +37165,16 @@
     <mergeCell ref="D722:D728"/>
     <mergeCell ref="C231:C233"/>
     <mergeCell ref="E231:E233"/>
-    <mergeCell ref="E1113:E1126"/>
     <mergeCell ref="D751:D752"/>
     <mergeCell ref="F751:F752"/>
+    <mergeCell ref="F1106:F1110"/>
     <mergeCell ref="C166:C205"/>
     <mergeCell ref="D753:D754"/>
     <mergeCell ref="C1053:C1056"/>
     <mergeCell ref="D647:D650"/>
     <mergeCell ref="F524:F528"/>
     <mergeCell ref="C914:C931"/>
-    <mergeCell ref="B1112:B1126"/>
     <mergeCell ref="F445:F449"/>
-    <mergeCell ref="D1112:D1126"/>
     <mergeCell ref="E180:E186"/>
     <mergeCell ref="F988:F989"/>
     <mergeCell ref="E571:E587"/>
@@ -37606,8 +37191,8 @@
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="G288:G289"/>
     <mergeCell ref="E103:E108"/>
-    <mergeCell ref="D1102:D1105"/>
     <mergeCell ref="D278:D283"/>
+    <mergeCell ref="F1102:F1105"/>
     <mergeCell ref="E219:E221"/>
     <mergeCell ref="F180:F181"/>
     <mergeCell ref="F240:F241"/>
@@ -37628,7 +37213,6 @@
     <mergeCell ref="D206:D212"/>
     <mergeCell ref="E529:E534"/>
     <mergeCell ref="D291:D296"/>
-    <mergeCell ref="F1122:F1126"/>
     <mergeCell ref="B1085:B1100"/>
     <mergeCell ref="F785:F787"/>
     <mergeCell ref="C785:C794"/>
@@ -37673,7 +37257,6 @@
     <mergeCell ref="D816:D821"/>
     <mergeCell ref="F315:F318"/>
     <mergeCell ref="D297:D302"/>
-    <mergeCell ref="D1109:D1111"/>
     <mergeCell ref="C695:C708"/>
     <mergeCell ref="E252:E257"/>
     <mergeCell ref="E959:E971"/>
@@ -37685,7 +37268,6 @@
     <mergeCell ref="C647:C657"/>
     <mergeCell ref="A309:A312"/>
     <mergeCell ref="D96:D102"/>
-    <mergeCell ref="D1106:D1108"/>
     <mergeCell ref="E689:E694"/>
     <mergeCell ref="C297:C308"/>
     <mergeCell ref="F406:F410"/>
